--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487670_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487670_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8959</v>
+        <v>8.169499999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5494</v>
+        <v>8.15</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3466</v>
+        <v>0.0195</v>
       </c>
       <c r="G2" t="n">
         <v>3.9868</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>0.133</v>
+        <v>0.4066</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6651</v>
+        <v>-0.0645</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7982</v>
+        <v>0.4711</v>
       </c>
       <c r="V2" t="n">
         <v>1.8358</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>L. VALERA VILLEGAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9691</v>
+        <v>3.6262</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3783</v>
+        <v>4.4287</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4092</v>
+        <v>-0.8025</v>
       </c>
       <c r="G3" t="n">
-        <v>2.289</v>
+        <v>2.4957</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7056</v>
+        <v>-1.0545</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4166</v>
+        <v>3.5502</v>
       </c>
       <c r="J3" t="n">
-        <v>2.624</v>
+        <v>3.437</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3398</v>
+        <v>-0.9474</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2842</v>
+        <v>4.3845</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.335</v>
+        <v>-0.9413</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3658</v>
+        <v>-0.1071</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7008</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3881</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.1344</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7463</v>
+        <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0204</v>
+        <v>0.7708</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4887</v>
+        <v>0.6782</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5317</v>
+        <v>0.0926</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0478</v>
+        <v>0.9418</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4</v>
+        <v>2.4477</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.3522</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. VALERA VILLEGAS</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7179</v>
+        <v>3.4954</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3296</v>
+        <v>4.1771</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6117</v>
+        <v>-0.6818</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4957</v>
+        <v>2.289</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0545</v>
+        <v>2.7056</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5502</v>
+        <v>-0.4166</v>
       </c>
       <c r="J4" t="n">
-        <v>3.437</v>
+        <v>2.624</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9474</v>
+        <v>2.3398</v>
       </c>
       <c r="L4" t="n">
-        <v>4.3845</v>
+        <v>0.2842</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9413</v>
+        <v>-0.335</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1071</v>
+        <v>0.3658</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.7008</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5821</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.1344</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8625</v>
+        <v>1.5466</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5791</v>
+        <v>1.2875</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2833</v>
+        <v>0.2591</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9418</v>
+        <v>0.0478</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4477</v>
+        <v>2.4</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.506</v>
+        <v>-2.3522</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1413</v>
+        <v>-0.5051</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.58</v>
+        <v>-0.7802</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4386</v>
+        <v>0.2751</v>
       </c>
       <c r="G5" t="n">
         <v>-1.1368</v>
@@ -844,13 +844,13 @@
         <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2492</v>
+        <v>0.8855</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8501</v>
+        <v>0.6499</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3991</v>
+        <v>0.2355</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2239</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2342</v>
+        <v>-2.4344</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1327</v>
+        <v>-1.3329</v>
       </c>
       <c r="F6" t="n">
         <v>-1.1015</v>
@@ -922,10 +922,10 @@
         <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09760000000000001</v>
+        <v>-0.1026</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0617</v>
+        <v>-0.1385</v>
       </c>
       <c r="U6" t="n">
         <v>0.0359</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.9527</v>
+        <v>-3.2352</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4964</v>
+        <v>-0.9968</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4564</v>
+        <v>-2.2383</v>
       </c>
       <c r="G7" t="n">
         <v>-2.4366</v>
@@ -1000,13 +1000,13 @@
         <v>1.5523</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8138</v>
+        <v>0.5313</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0329</v>
+        <v>0.5324</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2191</v>
+        <v>-0.0011</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9418</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ALMENARA SANABRIAS</t>
+          <t>A. ARMSTRONG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.3781</v>
+        <v>-3.6669</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9924</v>
+        <v>-2.0827</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3857</v>
+        <v>-1.5842</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.3907</v>
+        <v>-1.3404</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5067</v>
+        <v>-0.1392</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.884</v>
+        <v>-1.2012</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3262</v>
+        <v>-0.6106</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0618</v>
+        <v>0.0289</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.388</v>
+        <v>-0.6395</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0645</v>
+        <v>-0.7298</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5685</v>
+        <v>-0.1681</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.496</v>
+        <v>-0.5617</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5821</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9576</v>
+        <v>0.6735</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6662</v>
+        <v>0.6623</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2914</v>
+        <v>0.0112</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6119</v>
+        <v>-1.8358</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6119</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ARMSTRONG</t>
+          <t>A. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.5946</v>
+        <v>-3.7141</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6833</v>
+        <v>-1.4919</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9113</v>
+        <v>-2.2221</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3404</v>
+        <v>-3.3907</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1392</v>
+        <v>-0.5067</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2012</v>
+        <v>-2.884</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6106</v>
+        <v>-1.3262</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0289</v>
+        <v>0.0618</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6395</v>
+        <v>-1.388</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7298</v>
+        <v>-2.0645</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1681</v>
+        <v>-0.5685</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5617</v>
+        <v>-1.496</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2542</v>
+        <v>-0.2936</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0617</v>
+        <v>-0.1657</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3158</v>
+        <v>-0.1278</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8358</v>
+        <v>-0.6119</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8358</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.7519</v>
+        <v>-5.2053</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.0495</v>
+        <v>-3.7482</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7024</v>
+        <v>-1.4571</v>
       </c>
       <c r="G10" t="n">
         <v>-3.1369</v>
@@ -1234,13 +1234,13 @@
         <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8672</v>
+        <v>0.6794</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6662</v>
+        <v>0.6351</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.201</v>
+        <v>0.0443</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1657</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.469899999999998</v>
+        <v>-3.4699</v>
       </c>
       <c r="E11" t="n">
-        <v>6.323000000000002</v>
+        <v>6.3231</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.792999999999999</v>
+        <v>-9.792900000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-4.613599999999999</v>
@@ -1315,10 +1315,10 @@
         <v>5.0975</v>
       </c>
       <c r="T11" t="n">
-        <v>4.0767</v>
+        <v>4.076700000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0209</v>
+        <v>1.0208</v>
       </c>
       <c r="V11" t="n">
         <v>-3.9537</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.7402</v>
+        <v>3.0499</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4073</v>
+        <v>2.9078</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3329</v>
+        <v>0.1421</v>
       </c>
       <c r="G12" t="n">
         <v>2.1804</v>
@@ -1390,13 +1390,13 @@
         <v>2.1344</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2925</v>
+        <v>-0.9828</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9085</v>
+        <v>-0.408</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.384</v>
+        <v>-0.5748</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2821</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9573</v>
+        <v>1.721</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1909</v>
+        <v>2.0908</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2336</v>
+        <v>-0.3699</v>
       </c>
       <c r="G13" t="n">
         <v>0.2394</v>
@@ -1468,13 +1468,13 @@
         <v>1.5523</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3701</v>
+        <v>-0.6065</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.12</v>
+        <v>-0.2201</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2501</v>
+        <v>-0.3864</v>
       </c>
       <c r="V13" t="n">
         <v>1.506</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6016</v>
+        <v>1.2736</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4625</v>
+        <v>2.8619</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8608</v>
+        <v>-1.5883</v>
       </c>
       <c r="G14" t="n">
         <v>2.548</v>
@@ -1546,13 +1546,13 @@
         <v>0.194</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5462</v>
+        <v>0.2181</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0318</v>
+        <v>0.4312</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4856</v>
+        <v>-0.2131</v>
       </c>
       <c r="V14" t="n">
         <v>1.2239</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SANZ CÁMARA</t>
+          <t>L. BERMEJO ALCALDE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.724</v>
+        <v>0.3894</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3457</v>
+        <v>1.2825</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6217</v>
+        <v>-0.8932</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2484</v>
+        <v>0.3866</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0168</v>
+        <v>-0.4721</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7685</v>
+        <v>0.8586</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7841</v>
+        <v>1.3431</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6395</v>
+        <v>-0.6055</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1446</v>
+        <v>1.9486</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5358</v>
+        <v>-0.9565</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3773</v>
+        <v>0.1335</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.9131</v>
+        <v>-1.09</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3578</v>
+        <v>-0.1912</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6079</v>
+        <v>-0.0606</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2501</v>
+        <v>-0.1307</v>
       </c>
       <c r="V15" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. BERMEJO ALCALDE</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3076</v>
+        <v>0.3742</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2825</v>
+        <v>0.1683</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9749</v>
+        <v>0.2059</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3866</v>
+        <v>1.6052</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4721</v>
+        <v>-0.0882</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8586</v>
+        <v>1.6934</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3431</v>
+        <v>1.4071</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6055</v>
+        <v>0.103</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9486</v>
+        <v>1.3041</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9565</v>
+        <v>0.1981</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1335</v>
+        <v>-0.1912</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.09</v>
+        <v>0.3893</v>
       </c>
       <c r="P16" t="n">
-        <v>0.194</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R16" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.273</v>
+        <v>-0.4071</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0606</v>
+        <v>-0.1447</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2124</v>
+        <v>-0.2624</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.8462</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>M. BATLLE BERNARDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1373</v>
+        <v>0.1835</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2321</v>
+        <v>-0.3547</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3694</v>
+        <v>0.5382</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6052</v>
+        <v>-2.0696</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0882</v>
+        <v>0.6047</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6934</v>
+        <v>-2.6744</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4071</v>
+        <v>-1.4885</v>
       </c>
       <c r="K17" t="n">
-        <v>0.103</v>
+        <v>0.346</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3041</v>
+        <v>-1.8346</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1981</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1912</v>
+        <v>0.2587</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3893</v>
+        <v>-0.8398</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1642</v>
+        <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.644</v>
+        <v>-1.1647</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5451</v>
+        <v>-0.3438</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0989</v>
+        <v>-0.8209</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0478</v>
+        <v>2.4477</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8462</v>
+        <v>2.4477</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. BARROS CONDES</t>
+          <t>M. SANZ CÁMARA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0497</v>
+        <v>-0.0128</v>
       </c>
       <c r="E18" t="n">
-        <v>1.176</v>
+        <v>0.7451</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2257</v>
+        <v>-0.7579</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8566</v>
+        <v>0.2484</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0984</v>
+        <v>2.0168</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2418</v>
+        <v>-1.7685</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9028</v>
+        <v>1.7841</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9155</v>
+        <v>1.6395</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0127</v>
+        <v>0.1446</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0462</v>
+        <v>-1.5358</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1829</v>
+        <v>0.3773</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.229</v>
+        <v>-1.9131</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.194</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4302</v>
+        <v>-0.3791</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2434</v>
+        <v>0.0073</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6736</v>
+        <v>-0.3864</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2821</v>
+        <v>0.894</v>
       </c>
       <c r="W18" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.2821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. BATLLE BERNARDO</t>
+          <t>C. BARROS CONDES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1802</v>
+        <v>-0.1593</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5548999999999999</v>
+        <v>0.8757</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3747</v>
+        <v>-1.0349</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0696</v>
+        <v>0.8566</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6047</v>
+        <v>2.0984</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.6744</v>
+        <v>-1.2418</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4885</v>
+        <v>1.9028</v>
       </c>
       <c r="K19" t="n">
-        <v>0.346</v>
+        <v>1.9155</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.8346</v>
+        <v>-0.0127</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-1.0462</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2587</v>
+        <v>0.1829</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8398</v>
+        <v>-1.229</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9403</v>
+        <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5285</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.544</v>
+        <v>-0.0569</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9845</v>
+        <v>-0.4828</v>
       </c>
       <c r="V19" t="n">
-        <v>2.4477</v>
+        <v>-0.2821</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3065</v>
+        <v>-1.1425</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3634</v>
+        <v>-1.0631</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0568</v>
+        <v>-0.0794</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0428</v>
@@ -2014,13 +2014,13 @@
         <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7593</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5451</v>
+        <v>-0.2448</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2142</v>
+        <v>-0.3505</v>
       </c>
       <c r="V20" t="n">
         <v>0.6597</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4618</v>
+        <v>-2.2071</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.2785</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5401</v>
+        <v>-2.4856</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3385</v>
@@ -2092,13 +2092,13 @@
         <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7039</v>
+        <v>-0.4492</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1806</v>
+        <v>0.0196</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5233</v>
+        <v>-0.4688</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1657</v>
@@ -2125,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.469799999999999</v>
+        <v>3.4699</v>
       </c>
       <c r="E22" t="n">
         <v>9.7928</v>
@@ -2137,7 +2137,7 @@
         <v>4.613700000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2788</v>
+        <v>3.278799999999999</v>
       </c>
       <c r="I22" t="n">
         <v>1.3345</v>
@@ -2146,10 +2146,10 @@
         <v>11.3021</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3481</v>
+        <v>2.348099999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>8.9537</v>
+        <v>8.953699999999998</v>
       </c>
       <c r="M22" t="n">
         <v>-6.6884</v>
@@ -2170,13 +2170,13 @@
         <v>11.6419</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.0975</v>
+        <v>-5.097600000000001</v>
       </c>
       <c r="T22" t="n">
         <v>-1.0208</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.076700000000001</v>
+        <v>-4.0768</v>
       </c>
       <c r="V22" t="n">
         <v>3.9536</v>
